--- a/important_mails_2026-05-16.xlsx
+++ b/important_mails_2026-05-16.xlsx
@@ -1798,7 +1798,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>其他风险类</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1813,153 +1813,21 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Sat, 9 May 2026 08:34:05 +0000</t>
+          <t>Mon, 11 May 2026 11:38:29 +0000</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>donotreply@amazon.com</t>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 4.2026</t>
+          <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnungskorrektur) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnungskorrektur) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 9 May 2026 07:22:14 +0000</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 4.2026</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnungskorrektur) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnungskorrektur) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 9 May 2026 07:02:56 +0000</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.co.uk Merchant Credit Note for 4/2026</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Merchant Credit Note for the month of 4/2026 is now available in your Seller Central Account.
-To access your credit note, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your credit note.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 11 May 2026 11:38:29 +0000</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96
@@ -1968,39 +1836,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 05:42:00 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (zl4CmeMn1C)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2020,39 +1888,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2072,39 +1940,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2124,39 +1992,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2177,39 +2045,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 13:03:07 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2604121A02)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2229,39 +2097,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2281,39 +2149,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
@@ -2329,39 +2197,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 07:28:26 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (5NT+O11io4)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2381,39 +2249,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -2429,39 +2297,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2478,39 +2346,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2530,39 +2398,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2582,39 +2450,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2631,39 +2499,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
@@ -2678,39 +2546,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:45:41 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -2726,39 +2594,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:23:38 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2778,39 +2646,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2830,39 +2698,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2879,39 +2747,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2931,39 +2799,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2983,39 +2851,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3032,39 +2900,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3084,39 +2952,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -3130,39 +2998,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3182,39 +3050,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3231,39 +3099,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3279,39 +3147,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3331,39 +3199,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3380,41 +3248,41 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -3425,39 +3293,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3476,39 +3344,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3532,39 +3400,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3582,39 +3450,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3632,39 +3500,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 13:15:01 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3682,39 +3550,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:13:49 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3732,39 +3600,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:19:29 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3782,39 +3650,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 12:52:07 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -3830,39 +3698,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3880,39 +3748,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3930,39 +3798,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3972,39 +3840,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -4025,39 +3893,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4073,39 +3941,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4124,39 +3992,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -4167,39 +4035,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4218,39 +4086,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4269,39 +4137,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4320,39 +4188,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 03:03:00 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -4372,39 +4240,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 01:27:00 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20061337331] 对危险品分类提出异议</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商:您好!
 我们了解到您希望重新激活商品 ASIN: B0FCDRNTT8。
@@ -4433,39 +4301,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 10:07:05 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -4483,39 +4351,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:15:48 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4533,39 +4401,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:08:57 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4583,39 +4451,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 06:10:23 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12449434352] 【邀请函】诚邀您参与亚马逊卖家合规策略调研</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴，
 您好！
@@ -4629,39 +4497,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4679,40 +4547,40 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4729,40 +4597,40 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4779,39 +4647,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -4845,39 +4713,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4892,39 +4760,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -4940,39 +4808,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
@@ -4996,39 +4864,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -5044,6 +4912,138 @@
 Was this email helpful?
  https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
 SPC-USAmazon-1864773927693727</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 9 May 2026 08:34:05 +0000</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 4.2026</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnungskorrektur) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnungskorrektur) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 9 May 2026 07:22:14 +0000</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 4.2026</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnungskorrektur) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnungskorrektur) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 9 May 2026 07:02:56 +0000</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.co.uk Merchant Credit Note for 4/2026</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Merchant Credit Note for the month of 4/2026 is now available in your Seller Central Account.
+To access your credit note, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your credit note.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.co.uk</t>
         </is>
       </c>
     </row>

--- a/important_mails_2026-05-16.xlsx
+++ b/important_mails_2026-05-16.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>货件/库存类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -500,21 +500,69 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sat, 16 May 2026 04:51:55 +0000</t>
+          <t>Sat, 16 May 2026 17:10:29 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Create FBA removal order by 2026-05-28</t>
+          <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>¡Buenos días!
+Espero que te encuentres bien.
+Mi nombre es Luana Camargo y soy Business Developer en WORTEN Portugal y España, parte de Sonae, uno de los más grandes grupos empresariales en Portugal.
+Te envío este mensaje porque nos gustaría hacer una colaboración entre Weihai EU y el Marketplace de Worten.
+Sobre Worten.
+Somos líderes en el mercado portugués, con 200 tiendas alcanzamos más de 1.2 billones de euros en ventas, de los cuales el 20% vienen del online.
+En Portugal, Worten.pt es el sitio de comercio electrónico más visitado y con mejor desempeño, recibimos más visitas que los principales marketplaces del mundo, los que consideramos nuestra competencia. En compras online, el sitio web de Worten tiene el mayor tráfico de Portugal, más de 10 millones de visitas al mes.
+Es en www.worten.pt y www.worten.es donde puedes mirar nuestro Marketplace.
+Con más de 30 categorías, el Marketplace de Worten quiere ser la plataforma donde los clientes pueden encontrar todo lo que necesitan.
+Con la gran demanda que sentimos, tenemos la oportunidad de aumentar nuestra gama de productos, ¡y trabajar con las mejores empresas es nuestra prioridad !
+Worten Marketplace tiene una estrategia B2C, c</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 16 May 2026 04:51:55 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-05-28</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -538,39 +586,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:58:34 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -591,39 +639,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:50:26 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -646,39 +694,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 02:39:33 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (ZazNpo+O9J)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -704,39 +752,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 02:56:06 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -752,39 +800,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -809,39 +857,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:36:52 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -861,39 +909,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:51:22 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -909,39 +957,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:50:04 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -958,39 +1006,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:49:55 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1010,39 +1058,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:53:51 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -1059,39 +1107,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 07:42:16 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-de@amazon.com" &lt;fba-3p-buyability-improvement-de@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -1116,39 +1164,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 10:44:21 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-it@amazon.com" &lt;fba-3p-buyability-improvement-it@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -1173,40 +1221,40 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1221,40 +1269,40 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1268,40 +1316,40 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1315,39 +1363,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:52:25 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;store-news@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>EchoPlan Magnetic Blocks is still in your cart</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Still thinking about it? https://www.amazon.com/gp/cart/view.html?ref_=cor
 EchoPlan 200PCS Magnetic Blocks, Magnetic Building Blocks, Magnet Blocks Cubes, STEM Educational Stacking Magnet Toy for Kids Ages 3 4 5 6 7 8 9 10 11, Birthday Gifts for Boys and Girls, 1&amp;quot; Large Size
@@ -1368,39 +1416,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:07:42 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1415,39 +1463,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 03:00:00 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -1477,39 +1525,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 16:40:18 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -1537,39 +1585,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:51:48 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -1585,39 +1633,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 10:10:51 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>EPR Pay on Behalf charges for 2024 Amazon.co.uk sales</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1636,39 +1684,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 12:21:34 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -1690,39 +1738,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:22:50 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -1744,57 +1792,6 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 9 May 2026 16:23:48 +0000</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.ca
- Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
-Nous vous écrivons pour vous informer que votre Facture Expédié Par Amazon pour le mois de 4/2026 est maintenant disponible dans votre compte Seller Central.
-Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
-Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
-Pour toute question, contactez le Support Vendeur.
-Cordialement,
-Amazon.ca</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
@@ -3202,7 +3199,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3217,72 +3214,23 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
+          <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>donotreply@amazon.com</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 04/16/26 15:38 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 1,26.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éxit</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 11:37:14 +0000</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -3293,39 +3241,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3344,39 +3292,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -3400,39 +3348,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3450,39 +3398,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3500,39 +3448,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 13:15:01 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3550,39 +3498,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:13:49 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3600,39 +3548,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:19:29 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3650,39 +3598,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 12:52:07 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -3698,39 +3646,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3748,39 +3696,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3798,39 +3746,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3840,39 +3788,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -3893,39 +3841,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -3941,39 +3889,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -3992,39 +3940,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -4035,39 +3983,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4086,39 +4034,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4137,39 +4085,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4188,39 +4136,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 03:03:00 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -4240,39 +4188,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 01:27:00 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20061337331] 对危险品分类提出异议</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商:您好!
 我们了解到您希望重新激活商品 ASIN: B0FCDRNTT8。
@@ -4301,39 +4249,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 10:07:05 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -4351,39 +4299,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:15:48 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4401,39 +4349,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:08:57 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4451,39 +4399,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 06:10:23 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12449434352] 【邀请函】诚邀您参与亚马逊卖家合规策略调研</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴，
 您好！
@@ -4497,39 +4445,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4547,40 +4495,40 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4597,40 +4545,40 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4647,39 +4595,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -4713,39 +4661,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4760,39 +4708,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -4808,39 +4756,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
@@ -4864,39 +4812,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4912,6 +4860,57 @@
 Was this email helpful?
  https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
 SPC-USAmazon-1864773927693727</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 9 May 2026 16:23:48 +0000</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.ca
+ Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
+Nous vous écrivons pour vous informer que votre Facture Expédié Par Amazon pour le mois de 4/2026 est maintenant disponible dans votre compte Seller Central.
+Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
+Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
+Pour toute question, contactez le Support Vendeur.
+Cordialement,
+Amazon.ca</t>
         </is>
       </c>
     </row>
@@ -8911,7 +8910,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -8926,67 +8925,21 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
+          <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
+          <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
- Under the US INFORM Consumers Act, you are required to keep certain business information provided to Amazon current, including your name, address, phone number, email address, bank account information, and Tax ID number. You are also required to electronically certify to Amazon at least once per year that either you have provided any changes to your information or there have been no changes to this information.
- Review your account information and complete your electronic certification by following the instructions below to avoid disruption to your selling account. If you do not certify your information within 10 days of this notice, your account will be at risk of account deactivation, as required by the law.
- (Please disregard this notice if you have already certified your information and received an acknowledgment notice.)
- How do I certify my information and avoid account deactivation?
- Go to the INFORM Act Notice and Certification step in your ( Account Health page ).
- Follow the instructions on the page to review the required information, update it if necessary, and click the “Certify” button to certify that it is up-to-date.
- Please note that only the p</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 9 May 2026 04:43:42 +0000</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-05-21</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9010,39 +8963,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9065,39 +9018,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9121,39 +9074,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9177,39 +9130,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9230,39 +9183,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9284,39 +9237,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9339,39 +9292,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -9401,39 +9354,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -9482,39 +9435,39 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -9523,39 +9476,39 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
